--- a/Data/quest_network_sas.xlsx
+++ b/Data/quest_network_sas.xlsx
@@ -470,10 +470,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
+      <c r="A2" t="n">
+        <v>188</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -502,10 +500,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -534,10 +530,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A4" t="n">
+        <v>158</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -566,10 +560,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="A5" t="n">
+        <v>152</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -598,10 +590,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
+      <c r="A6" t="n">
+        <v>145</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -630,10 +620,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+      <c r="A7" t="n">
+        <v>139</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -662,10 +650,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A8" t="n">
+        <v>51</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -694,10 +680,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A9" t="n">
+        <v>17</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -726,10 +710,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A10" t="n">
+        <v>16</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -758,10 +740,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A11" t="n">
+        <v>15</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -790,10 +770,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A12" t="n">
+        <v>14</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -822,10 +800,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A13" t="n">
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -854,10 +830,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A14" t="n">
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -886,10 +860,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A15" t="n">
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -918,10 +890,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A16" t="n">
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -950,10 +920,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A17" t="n">
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -982,10 +950,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A18" t="n">
+        <v>8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1014,10 +980,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A19" t="n">
+        <v>7</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1046,10 +1010,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A20" t="n">
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1078,10 +1040,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A21" t="n">
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1110,10 +1070,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A22" t="n">
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1142,10 +1100,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A23" t="n">
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1174,10 +1130,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A24" t="n">
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1206,10 +1160,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1238,10 +1190,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A26" t="n">
+        <v>18</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1270,10 +1220,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A27" t="n">
+        <v>19</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1302,10 +1250,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A28" t="n">
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1334,10 +1280,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A29" t="n">
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1366,10 +1310,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A30" t="n">
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1398,10 +1340,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A31" t="n">
+        <v>23</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1430,10 +1370,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A32" t="n">
+        <v>24</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1462,10 +1400,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A33" t="n">
+        <v>26</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1494,10 +1430,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A34" t="n">
+        <v>25</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1526,10 +1460,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A35" t="n">
+        <v>27</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1558,10 +1490,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A36" t="n">
+        <v>28</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1590,10 +1520,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A37" t="n">
+        <v>29</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1622,10 +1550,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A38" t="n">
+        <v>30</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1654,10 +1580,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A39" t="n">
+        <v>31</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1686,10 +1610,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A40" t="n">
+        <v>32</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1718,10 +1640,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A41" t="n">
+        <v>33</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1750,10 +1670,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A42" t="n">
+        <v>34</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1782,10 +1700,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A43" t="n">
+        <v>35</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1814,10 +1730,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A44" t="n">
+        <v>36</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1846,10 +1760,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A45" t="n">
+        <v>37</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1878,10 +1790,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A46" t="n">
+        <v>39</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1910,10 +1820,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A47" t="n">
+        <v>40</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1942,10 +1850,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A48" t="n">
+        <v>42</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1974,10 +1880,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A49" t="n">
+        <v>43</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2006,10 +1910,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A50" t="n">
+        <v>44</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2038,10 +1940,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="A51" t="n">
+        <v>45</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2070,10 +1970,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A52" t="n">
+        <v>46</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2102,10 +2000,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A53" t="n">
+        <v>47</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2134,10 +2030,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A54" t="n">
+        <v>48</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2166,10 +2060,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A55" t="n">
+        <v>49</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2198,10 +2090,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A56" t="n">
+        <v>50</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2230,10 +2120,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="A57" t="n">
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2262,10 +2150,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A58" t="n">
+        <v>60</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2294,10 +2180,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A59" t="n">
+        <v>52</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2326,10 +2210,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="A60" t="n">
+        <v>53</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2358,10 +2240,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A61" t="n">
+        <v>55</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2390,10 +2270,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A62" t="n">
+        <v>54</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2422,10 +2300,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="A63" t="n">
+        <v>59</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2454,10 +2330,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="A64" t="n">
+        <v>58</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2486,10 +2360,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A65" t="n">
+        <v>57</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2518,10 +2390,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="A66" t="n">
+        <v>61</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2550,10 +2420,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A67" t="n">
+        <v>62</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2582,10 +2450,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A68" t="n">
+        <v>63</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2614,10 +2480,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="A69" t="n">
+        <v>64</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2646,10 +2510,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="A70" t="n">
+        <v>65</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2678,10 +2540,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="A71" t="n">
+        <v>66</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2710,10 +2570,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="A72" t="n">
+        <v>67</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2742,10 +2600,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="A73" t="n">
+        <v>68</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2774,10 +2630,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A74" t="n">
+        <v>69</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2806,10 +2660,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="A75" t="n">
+        <v>70</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2838,10 +2690,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="A76" t="n">
+        <v>71</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2870,10 +2720,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="A77" t="n">
+        <v>72</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2902,10 +2750,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="A78" t="n">
+        <v>73</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2934,10 +2780,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="A79" t="n">
+        <v>74</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2966,10 +2810,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A80" t="n">
+        <v>75</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2998,10 +2840,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="A81" t="n">
+        <v>76</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3030,10 +2870,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A82" t="n">
+        <v>77</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3062,10 +2900,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A83" t="n">
+        <v>78</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3094,10 +2930,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="A84" t="n">
+        <v>79</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3126,10 +2960,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="A85" t="n">
+        <v>81</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3158,10 +2990,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A86" t="n">
+        <v>82</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3190,10 +3020,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="A87" t="n">
+        <v>83</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3222,10 +3050,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="A88" t="n">
+        <v>84</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3254,10 +3080,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="A89" t="n">
+        <v>85</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3286,10 +3110,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="A90" t="n">
+        <v>86</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3318,10 +3140,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="A91" t="n">
+        <v>87</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3350,10 +3170,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A92" t="n">
+        <v>88</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3382,10 +3200,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="A93" t="n">
+        <v>89</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3414,10 +3230,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="A94" t="n">
+        <v>90</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3446,10 +3260,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="A95" t="n">
+        <v>91</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3478,10 +3290,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="A96" t="n">
+        <v>92</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3510,10 +3320,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="A97" t="n">
+        <v>93</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3542,10 +3350,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="A98" t="n">
+        <v>94</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3574,10 +3380,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="A99" t="n">
+        <v>95</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3606,10 +3410,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="A100" t="n">
+        <v>96</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3638,10 +3440,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="A101" t="n">
+        <v>97</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3670,10 +3470,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="A102" t="n">
+        <v>98</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3702,10 +3500,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="A103" t="n">
+        <v>99</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3734,10 +3530,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="A104" t="n">
+        <v>100</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3766,10 +3560,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="A105" t="n">
+        <v>111</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3798,10 +3590,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+      <c r="A106" t="n">
+        <v>112</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3830,10 +3620,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="A107" t="n">
+        <v>113</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3862,10 +3650,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="A108" t="n">
+        <v>114</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3894,10 +3680,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="A109" t="n">
+        <v>115</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3926,10 +3710,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="A110" t="n">
+        <v>116</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -3958,10 +3740,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="A111" t="n">
+        <v>117</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -3990,10 +3770,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="A112" t="n">
+        <v>118</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4022,10 +3800,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A113" t="n">
+        <v>119</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4054,10 +3830,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="A114" t="n">
+        <v>120</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4086,10 +3860,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="A115" t="n">
+        <v>121</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4118,10 +3890,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="A116" t="n">
+        <v>122</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4150,10 +3920,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="A117" t="n">
+        <v>123</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4182,10 +3950,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="A118" t="n">
+        <v>124</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4214,10 +3980,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="A119" t="n">
+        <v>125</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4246,10 +4010,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="A120" t="n">
+        <v>126</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4278,10 +4040,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="A121" t="n">
+        <v>127</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -4310,10 +4070,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="A122" t="n">
+        <v>128</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -4342,10 +4100,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="A123" t="n">
+        <v>129</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -4374,10 +4130,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="A124" t="n">
+        <v>131</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -4406,10 +4160,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="A125" t="n">
+        <v>132</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -4438,10 +4190,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="A126" t="n">
+        <v>133</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -4470,10 +4220,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="A127" t="n">
+        <v>134</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -4502,10 +4250,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="A128" t="n">
+        <v>135</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -4534,10 +4280,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="A129" t="n">
+        <v>136</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -4566,10 +4310,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="A130" t="n">
+        <v>137</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -4598,10 +4340,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A131" t="n">
+        <v>41</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -4630,10 +4370,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A132" t="n">
+        <v>38</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -4662,10 +4400,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="A133" t="n">
+        <v>130</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4694,10 +4430,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="A134" t="n">
+        <v>141</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -4726,10 +4460,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+      <c r="A135" t="n">
+        <v>161</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -4758,10 +4490,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="A136" t="n">
+        <v>175</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -4790,10 +4520,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="A137" t="n">
+        <v>80</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -4822,10 +4550,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="A138" t="n">
+        <v>138</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4854,10 +4580,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A139" t="n">
+        <v>140</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -4886,10 +4610,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="A140" t="n">
+        <v>143</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -4918,10 +4640,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="A141" t="n">
+        <v>142</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -4950,10 +4670,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="A142" t="n">
+        <v>146</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -4982,10 +4700,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="A143" t="n">
+        <v>144</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5014,10 +4730,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A144" t="n">
+        <v>101</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -5046,10 +4760,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>100.3</t>
-        </is>
+      <c r="A145" t="n">
+        <v>103</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -5078,10 +4790,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>100.2</t>
-        </is>
+      <c r="A146" t="n">
+        <v>102</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -5110,10 +4820,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
+      <c r="A147" t="n">
+        <v>106</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5142,10 +4850,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>100.4</t>
-        </is>
+      <c r="A148" t="n">
+        <v>104</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -5174,10 +4880,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="A149" t="n">
+        <v>105</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -5206,10 +4910,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>100.8</t>
-        </is>
+      <c r="A150" t="n">
+        <v>108</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -5238,10 +4940,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>100.7</t>
-        </is>
+      <c r="A151" t="n">
+        <v>107</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -5270,10 +4970,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="A152" t="n">
+        <v>109</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -5302,10 +5000,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="A153" t="n">
+        <v>148</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -5334,10 +5030,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="A154" t="n">
+        <v>147</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -5366,10 +5060,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="A155" t="n">
+        <v>149</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -5398,10 +5090,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="A156" t="n">
+        <v>110</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -5430,10 +5120,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="A157" t="n">
+        <v>153</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -5462,10 +5150,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="A158" t="n">
+        <v>151</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -5494,10 +5180,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+      <c r="A159" t="n">
+        <v>150</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -5526,10 +5210,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="A160" t="n">
+        <v>154</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -5558,10 +5240,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="A161" t="n">
+        <v>180</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -5590,10 +5270,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A162" t="n">
+        <v>170</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -5622,10 +5300,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="A163" t="n">
+        <v>155</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -5654,10 +5330,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="A164" t="n">
+        <v>160</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -5686,10 +5360,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="A165" t="n">
+        <v>156</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -5718,10 +5390,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="A166" t="n">
+        <v>157</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -5750,10 +5420,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="A167" t="n">
+        <v>159</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -5782,10 +5450,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
+      <c r="A168" t="n">
+        <v>163</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -5814,10 +5480,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="A169" t="n">
+        <v>162</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -5846,10 +5510,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="A170" t="n">
+        <v>168</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -5878,10 +5540,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+      <c r="A171" t="n">
+        <v>164</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -5910,10 +5570,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="A172" t="n">
+        <v>165</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -5942,10 +5600,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="A173" t="n">
+        <v>167</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -5974,10 +5630,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="A174" t="n">
+        <v>166</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -6006,10 +5660,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A175" t="n">
+        <v>169</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6038,10 +5690,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="A176" t="n">
+        <v>173</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6070,10 +5720,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
+      <c r="A177" t="n">
+        <v>174</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6102,10 +5750,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A178" t="n">
+        <v>171</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -6134,10 +5780,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="A179" t="n">
+        <v>172</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6166,10 +5810,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
+      <c r="A180" t="n">
+        <v>176</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -6198,10 +5840,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="A181" t="n">
+        <v>177</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -6230,10 +5870,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="A182" t="n">
+        <v>178</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -6262,10 +5900,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="A183" t="n">
+        <v>179</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -6294,10 +5930,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
+      <c r="A184" t="n">
+        <v>181</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -6326,10 +5960,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+      <c r="A185" t="n">
+        <v>184</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -6358,10 +5990,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+      <c r="A186" t="n">
+        <v>185</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -6390,10 +6020,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="A187" t="n">
+        <v>186</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -6422,10 +6050,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
+      <c r="A188" t="n">
+        <v>187</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -6454,10 +6080,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
+      <c r="A189" t="n">
+        <v>182</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -6486,10 +6110,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="A190" t="n">
+        <v>183</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -6533,7 +6155,7 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
@@ -6566,20 +6188,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A2" t="n">
+        <v>17</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>Dragon Slayer I</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="C2" t="n">
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6591,20 +6209,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A3" t="n">
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="C3" t="n">
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6616,20 +6230,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A4" t="n">
+        <v>19</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Lost City</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="C4" t="n">
+        <v>22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6641,20 +6251,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A5" t="n">
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Merlin's Crystal</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="C5" t="n">
+        <v>22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6666,20 +6272,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A6" t="n">
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Shield of Arrav</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="C6" t="n">
+        <v>22</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6697,10 +6299,8 @@
           <t>Alfred Grimhand's Barcrawl</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="C7" t="n">
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6712,20 +6312,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A8" t="n">
+        <v>21</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Merlin's Crystal</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="C8" t="n">
+        <v>30</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6737,20 +6333,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A9" t="n">
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="C9" t="n">
+        <v>39</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6762,20 +6354,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A10" t="n">
+        <v>38</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Biohazard</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="C10" t="n">
+        <v>42</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6787,20 +6375,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A11" t="n">
+        <v>18</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="C11" t="n">
+        <v>45</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6812,20 +6396,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A12" t="n">
+        <v>18</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="C12" t="n">
+        <v>48</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6837,20 +6417,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A13" t="n">
+        <v>24</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Family Crest</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C13" t="n">
+        <v>50</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6862,20 +6438,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A14" t="n">
+        <v>22</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Heroes' Quest</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C14" t="n">
+        <v>50</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6887,20 +6459,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A15" t="n">
+        <v>41</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Shilo Village</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C15" t="n">
+        <v>50</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6912,20 +6480,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A16" t="n">
+        <v>42</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Underground Pass</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C16" t="n">
+        <v>50</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6937,20 +6501,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A17" t="n">
+        <v>37</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Waterfall Quest</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C17" t="n">
+        <v>50</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6962,20 +6522,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A18" t="n">
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="C18" t="n">
+        <v>60</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6987,20 +6543,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A19" t="n">
+        <v>57</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Troll Stronghold</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="C19" t="n">
+        <v>60</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7012,20 +6564,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A20" t="n">
+        <v>54</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="C20" t="n">
+        <v>55</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -7037,20 +6585,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A21" t="n">
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>The Restless Ghost</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="C21" t="n">
+        <v>55</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -7062,20 +6606,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A22" t="n">
+        <v>42</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Underground Pass</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="C22" t="n">
+        <v>59</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -7087,20 +6627,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A23" t="n">
+        <v>39</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Jungle Potion</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="C23" t="n">
+        <v>58</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -7112,20 +6648,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="A24" t="n">
+        <v>56</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Death Plateau</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="C24" t="n">
+        <v>57</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7137,20 +6669,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A25" t="n">
+        <v>18</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="C25" t="n">
+        <v>61</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7162,20 +6690,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A26" t="n">
+        <v>54</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="C26" t="n">
+        <v>61</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -7193,10 +6717,8 @@
           <t>Alfred Grimhand's Barcrawl</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="C27" t="n">
+        <v>63</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -7208,20 +6730,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A28" t="n">
+        <v>62</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>The Fremennik Trials</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="C28" t="n">
+        <v>64</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7233,20 +6751,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A29" t="n">
+        <v>22</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Heroes' Quest</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="C29" t="n">
+        <v>64</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7258,20 +6772,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A30" t="n">
+        <v>40</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>The Grand Tree</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="C30" t="n">
+        <v>65</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7283,20 +6793,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A31" t="n">
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Tree Gnome Village</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="C31" t="n">
+        <v>65</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7308,20 +6814,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A32" t="n">
+        <v>54</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="C32" t="n">
+        <v>66</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7333,20 +6835,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A33" t="n">
+        <v>57</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Troll Stronghold</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="C33" t="n">
+        <v>67</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7358,20 +6856,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A34" t="n">
+        <v>55</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Nature Spirit</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="C34" t="n">
+        <v>68</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -7383,20 +6877,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A35" t="n">
+        <v>54</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="C35" t="n">
+        <v>69</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7408,20 +6898,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A36" t="n">
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>The Restless Ghost</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="C36" t="n">
+        <v>69</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -7433,20 +6919,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="A37" t="n">
+        <v>59</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Regicide</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="C37" t="n">
+        <v>70</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -7458,20 +6940,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A38" t="n">
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Waterfall Quest</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="C38" t="n">
+        <v>70</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7483,20 +6961,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A39" t="n">
+        <v>54</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="C39" t="n">
+        <v>71</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7508,20 +6982,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A40" t="n">
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>The Restless Ghost</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="C40" t="n">
+        <v>71</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7533,20 +7003,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A41" t="n">
+        <v>51</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Rune Mysteries</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="C41" t="n">
+        <v>72</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7558,20 +7024,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A42" t="n">
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Shilo Village</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="C42" t="n">
+        <v>72</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7583,20 +7045,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A43" t="n">
+        <v>46</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Dwarf Cannon</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="C43" t="n">
+        <v>74</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7608,20 +7066,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A44" t="n">
+        <v>26</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Fishing Contest</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="C44" t="n">
+        <v>74</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7633,20 +7087,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A45" t="n">
+        <v>48</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>The Dig Site</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="C45" t="n">
+        <v>77</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7658,20 +7108,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A46" t="n">
+        <v>28</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Temple of Ikov</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="C46" t="n">
+        <v>77</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7683,20 +7129,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A47" t="n">
+        <v>44</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>The Tourist Trap</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="C47" t="n">
+        <v>77</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7708,20 +7150,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A48" t="n">
+        <v>57</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Troll Stronghold</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="C48" t="n">
+        <v>77</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7733,20 +7171,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A49" t="n">
+        <v>54</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="C49" t="n">
+        <v>77</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7758,20 +7192,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A50" t="n">
+        <v>37</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Waterfall Quest</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="C50" t="n">
+        <v>77</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7783,20 +7213,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A51" t="n">
+        <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Gertrude's Cat</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="C51" t="n">
+        <v>78</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7808,20 +7234,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A52" t="n">
+        <v>15</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Goblin Diplomacy</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="C52" t="n">
+        <v>81</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7833,20 +7255,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A53" t="n">
+        <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Rune Mysteries</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="C53" t="n">
+        <v>81</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7858,20 +7276,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A54" t="n">
+        <v>12</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Black Knights' Fortress</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="C54" t="n">
+        <v>83</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7883,20 +7297,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A55" t="n">
+        <v>18</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="C55" t="n">
+        <v>83</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7908,20 +7318,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A56" t="n">
+        <v>52</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Big Chompy Bird Hunting</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="C56" t="n">
+        <v>84</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7933,20 +7339,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="A57" t="n">
+        <v>70</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Roving Elves</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="C57" t="n">
+        <v>84</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7958,20 +7360,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A58" t="n">
+        <v>34</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Sheep Herder</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="C58" t="n">
+        <v>84</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7983,20 +7381,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A59" t="n">
+        <v>82</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>The Giant Dwarf</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="C59" t="n">
+        <v>85</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8008,20 +7402,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A60" t="n">
+        <v>26</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Fishing Contest</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="C60" t="n">
+        <v>85</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8033,20 +7423,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A61" t="n">
+        <v>69</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Creature of Fenkenstrain</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="C61" t="n">
+        <v>86</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8058,20 +7444,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A62" t="n">
+        <v>78</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Icthlarin's Little Helper</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="C62" t="n">
+        <v>87</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8083,20 +7465,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="A63" t="n">
+        <v>81</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>The Lost Tribe</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="C63" t="n">
+        <v>88</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8108,20 +7486,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A64" t="n">
+        <v>54</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="C64" t="n">
+        <v>88</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8133,20 +7507,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="A65" t="n">
+        <v>83</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Recruitment Drive</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="C65" t="n">
+        <v>88</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8164,10 +7534,8 @@
           <t>Started:Enter the Abyss</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="C66" t="n">
+        <v>88</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8179,20 +7547,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="A67" t="n">
+        <v>84</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Mourning's End Part I</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="C67" t="n">
+        <v>89</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8204,20 +7568,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A68" t="n">
+        <v>54</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="C68" t="n">
+        <v>90</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8229,20 +7589,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="A69" t="n">
+        <v>80</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Zogre Flesh Eaters</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="C69" t="n">
+        <v>90</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8254,20 +7610,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A70" t="n">
+        <v>2</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="C70" t="n">
+        <v>91</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8279,20 +7631,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="A71" t="n">
+        <v>76</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>The Golem</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="C71" t="n">
+        <v>91</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8304,20 +7652,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A72" t="n">
+        <v>54</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="C72" t="n">
+        <v>92</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8329,20 +7673,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A73" t="n">
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>The Restless Ghost</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="C73" t="n">
+        <v>92</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8354,20 +7694,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A74" t="n">
+        <v>78</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Icthlarin's Little Helper</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="C74" t="n">
+        <v>93</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8379,20 +7715,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A75" t="n">
+        <v>82</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Started:The Giant Dwarf</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="C75" t="n">
+        <v>93</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8404,20 +7736,16 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A76" t="n">
+        <v>11</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Doric's Quest</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="C76" t="n">
+        <v>95</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8435,10 +7763,8 @@
           <t>Enter the Abyss</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="C77" t="n">
+        <v>95</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8450,20 +7776,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A78" t="n">
+        <v>57</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Troll Stronghold</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="C78" t="n">
+        <v>95</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8475,20 +7797,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A79" t="n">
+        <v>88</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Wanted!</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="C79" t="n">
+        <v>95</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8500,20 +7818,16 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A80" t="n">
+        <v>16</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Pirate's Treasure</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="C80" t="n">
+        <v>98</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8525,20 +7839,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="A81" t="n">
+        <v>90</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Rum Deal</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="C81" t="n">
+        <v>98</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8550,20 +7860,16 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A82" t="n">
+        <v>19</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Lost City</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="C82" t="n">
+        <v>99</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8575,20 +7881,16 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A83" t="n">
+        <v>55</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Nature Spirit</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="C83" t="n">
+        <v>99</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,20 +7902,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="A84" t="n">
+        <v>110</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Defeating the Culinaromancer</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="C84" t="n">
+        <v>100</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8625,20 +7923,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="A85" t="n">
+        <v>68</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>In Search of the Myreque</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="C85" t="n">
+        <v>111</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8650,20 +7944,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="A86" t="n">
+        <v>86</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Garden of Tranquillity</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="C86" t="n">
+        <v>114</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8675,20 +7965,16 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="A87" t="n">
+        <v>72</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>One Small Favour</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="C87" t="n">
+        <v>114</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8700,20 +7986,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="A88" t="n">
+        <v>64</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Throne of Miscellania</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="C88" t="n">
+        <v>115</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8725,20 +8007,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="A89" t="n">
+        <v>81</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>The Lost Tribe</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="C89" t="n">
+        <v>116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8750,20 +8028,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A90" t="n">
+        <v>18</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="C90" t="n">
+        <v>117</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8775,20 +8049,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="A91" t="n">
+        <v>99</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Fairytale I - Growing Pains</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="C91" t="n">
+        <v>117</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8800,20 +8070,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A92" t="n">
+        <v>62</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>The Fremennik Trials</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="C92" t="n">
+        <v>118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8825,20 +8091,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A93" t="n">
+        <v>19</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Lost City</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="C93" t="n">
+        <v>118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8850,20 +8112,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A94" t="n">
+        <v>51</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Rune Mysteries</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="C94" t="n">
+        <v>118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8875,20 +8133,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A95" t="n">
+        <v>41</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Shilo Village</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="C95" t="n">
+        <v>118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8900,20 +8154,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A96" t="n">
+        <v>40</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>The Grand Tree</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="C96" t="n">
+        <v>119</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8925,20 +8175,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="A97" t="n">
+        <v>111</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>In Aid of the Myreque</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="C97" t="n">
+        <v>120</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8950,20 +8196,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A98" t="n">
+        <v>36</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Sea Slug</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="C98" t="n">
+        <v>121</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8975,20 +8217,16 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A99" t="n">
+        <v>88</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Wanted!</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="C99" t="n">
+        <v>121</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9000,20 +8238,16 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="A100" t="n">
+        <v>53</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Elemental Workshop I</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="C100" t="n">
+        <v>122</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9025,20 +8259,16 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A101" t="n">
+        <v>60</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Eadgar's Ruse</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="C101" t="n">
+        <v>123</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9050,20 +8280,16 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A102" t="n">
+        <v>75</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>The Feud</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="C102" t="n">
+        <v>123</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9075,20 +8301,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A103" t="n">
+        <v>39</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Jungle Potion</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="C103" t="n">
+        <v>123</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9100,20 +8322,16 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A104" t="n">
+        <v>7</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Ernest the Chicken</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="C104" t="n">
+        <v>126</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9125,20 +8343,16 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A105" t="n">
+        <v>54</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Priest in Peril</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="C105" t="n">
+        <v>126</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9150,20 +8364,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A106" t="n">
+        <v>3</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>The Restless Ghost</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="C106" t="n">
+        <v>126</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9175,20 +8385,16 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A107" t="n">
+        <v>10</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Prince Ali Rescue</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="C107" t="n">
+        <v>127</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9200,20 +8406,16 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A108" t="n">
+        <v>78</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Icthlarin's Little Helper</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="C108" t="n">
+        <v>127</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9225,20 +8427,16 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A109" t="n">
+        <v>62</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>The Fremennik Trials</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="C109" t="n">
+        <v>129</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9250,20 +8448,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="A110" t="n">
+        <v>98</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Cabin Fever</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="C110" t="n">
+        <v>131</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9275,20 +8469,16 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A111" t="n">
+        <v>69</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Creature of Fenkenstrain</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="C111" t="n">
+        <v>131</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9300,20 +8490,16 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>100.4</t>
-        </is>
+      <c r="A112" t="n">
+        <v>104</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing Pirate Pete</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="C112" t="n">
+        <v>131</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9325,20 +8511,16 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A113" t="n">
+        <v>51</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Rune Mysteries</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="C113" t="n">
+        <v>132</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9350,20 +8532,16 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A114" t="n">
+        <v>62</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>The Fremennik Trials</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="C114" t="n">
+        <v>133</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9375,20 +8553,16 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="A115" t="n">
+        <v>116</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Death to the Dorgeshuun</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="C115" t="n">
+        <v>134</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9400,20 +8574,16 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A116" t="n">
+        <v>48</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>The Dig Site</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="C116" t="n">
+        <v>134</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9425,20 +8595,16 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A117" t="n">
+        <v>82</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>The Giant Dwarf</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="C117" t="n">
+        <v>134</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9450,20 +8616,16 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A118" t="n">
+        <v>60</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Eadgar's Ruse</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="C118" t="n">
+        <v>135</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9475,20 +8637,16 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="A119" t="n">
+        <v>118</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Lunar Diplomacy</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="C119" t="n">
+        <v>135</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9500,20 +8658,16 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A120" t="n">
+        <v>18</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="C120" t="n">
+        <v>136</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9525,20 +8679,16 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A121" t="n">
+        <v>20</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Witch's House</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="C121" t="n">
+        <v>136</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9550,20 +8700,16 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A122" t="n">
+        <v>12</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Black Knights' Fortress</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="C122" t="n">
+        <v>137</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9575,20 +8721,16 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A123" t="n">
+        <v>30</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Holy Grail</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="C123" t="n">
+        <v>137</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9600,20 +8742,16 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A124" t="n">
+        <v>47</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Murder Mystery</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="C124" t="n">
+        <v>137</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9625,20 +8763,16 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="A125" t="n">
+        <v>72</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>One Small Favour</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="C125" t="n">
+        <v>137</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9650,20 +8784,16 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A126" t="n">
+        <v>39</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Jungle Potion</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="C126" t="n">
+        <v>41</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9675,20 +8805,16 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A127" t="n">
+        <v>35</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Plague City</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="C127" t="n">
+        <v>38</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9700,20 +8826,16 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A128" t="n">
+        <v>62</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>The Fremennik Trials</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="C128" t="n">
+        <v>141</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9725,20 +8847,16 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A129" t="n">
+        <v>63</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Horror from the Deep</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="C129" t="n">
+        <v>141</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9750,20 +8868,16 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="A130" t="n">
+        <v>113</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Rag and Bone Man I</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="C130" t="n">
+        <v>141</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9781,10 +8895,8 @@
           <t>Skippy and the Mogres</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="C131" t="n">
+        <v>141</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9796,20 +8908,16 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A132" t="n">
+        <v>69</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Started:Creature of Fenkenstrain</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="C132" t="n">
+        <v>141</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9821,20 +8929,16 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A133" t="n">
+        <v>37</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Started:Waterfall Quest</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="C133" t="n">
+        <v>141</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9846,20 +8950,16 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="A134" t="n">
+        <v>80</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Started:Zogre Flesh Eaters</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="C134" t="n">
+        <v>141</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9871,20 +8971,16 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A135" t="n">
+        <v>170</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Defender of Varrock</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C135" t="n">
+        <v>175</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9896,20 +8992,16 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="A136" t="n">
+        <v>168</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>The Path of Glouphrie</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C136" t="n">
+        <v>175</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9921,20 +9013,16 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A137" t="n">
+        <v>32</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Fight Arena</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C137" t="n">
+        <v>175</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9946,20 +9034,16 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="A138" t="n">
+        <v>135</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Dream Mentor</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C138" t="n">
+        <v>175</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9971,20 +9055,16 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="A139" t="n">
+        <v>96</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>The Hand in the Sand</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C139" t="n">
+        <v>175</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9996,20 +9076,16 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A140" t="n">
+        <v>88</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Wanted!</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C140" t="n">
+        <v>175</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10021,20 +9097,16 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="A141" t="n">
+        <v>162</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Temple of the Eye</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C141" t="n">
+        <v>175</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10046,20 +9118,16 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="A142" t="n">
+        <v>79</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Tears of Guthix</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C142" t="n">
+        <v>175</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10071,20 +9139,16 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A143" t="n">
+        <v>55</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Nature Spirit</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C143" t="n">
+        <v>175</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10096,20 +9160,16 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="A144" t="n">
+        <v>87</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>A Tail of Two Cats</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="C144" t="n">
+        <v>175</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10121,20 +9181,16 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A145" t="n">
+        <v>52</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Big Chompy Bird Hunting</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="C145" t="n">
+        <v>80</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10146,20 +9202,16 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A146" t="n">
+        <v>39</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Jungle Potion</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="C146" t="n">
+        <v>80</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10171,20 +9223,16 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="A147" t="n">
+        <v>124</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Enlightened Journey</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="C147" t="n">
+        <v>138</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10196,20 +9244,16 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A148" t="n">
+        <v>119</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>The Eyes of Glouphrie</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="C148" t="n">
+        <v>138</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10221,20 +9265,16 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>100.7</t>
-        </is>
+      <c r="A149" t="n">
+        <v>107</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing King Awowogei</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="C149" t="n">
+        <v>138</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10246,20 +9286,16 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A150" t="n">
+        <v>57</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Troll Stronghold</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="C150" t="n">
+        <v>138</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10271,20 +9307,16 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="A151" t="n">
+        <v>45</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Watchtower</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="C151" t="n">
+        <v>138</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10296,20 +9328,16 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="A152" t="n">
+        <v>152</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>X Marks the Spot</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="C152" t="n">
+        <v>140</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10321,20 +9349,16 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A153" t="n">
+        <v>140</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Client of Kourend</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="C153" t="n">
+        <v>143</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10346,20 +9370,16 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A154" t="n">
+        <v>48</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>The Dig Site</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="C154" t="n">
+        <v>142</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10371,20 +9391,16 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="A155" t="n">
+        <v>126</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Animal Magnetism</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C155" t="n">
+        <v>146</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10402,10 +9418,8 @@
           <t>Barbarian Firemaking</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C156" t="n">
+        <v>146</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10417,20 +9431,16 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="A157" t="n">
+        <v>142</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Bone Voyage</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C157" t="n">
+        <v>146</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10442,20 +9452,16 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A158" t="n">
+        <v>140</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Client of Kourend</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C158" t="n">
+        <v>146</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10467,20 +9473,16 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="A159" t="n">
+        <v>135</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Dream Mentor</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C159" t="n">
+        <v>146</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10492,20 +9494,16 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="A160" t="n">
+        <v>71</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Ghosts Ahoy</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C160" t="n">
+        <v>146</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10517,20 +9515,16 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A161" t="n">
+        <v>50</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Legends' Quest</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C161" t="n">
+        <v>146</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10542,20 +9536,16 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="A162" t="n">
+        <v>87</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>A Tail of Two Cats</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="C162" t="n">
+        <v>146</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10567,20 +9557,16 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A163" t="n">
+        <v>140</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Client of Kourend</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="C163" t="n">
+        <v>144</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10592,20 +9578,16 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A164" t="n">
+        <v>1</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Cook's Assistant</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="C164" t="n">
+        <v>101</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10617,20 +9599,16 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A165" t="n">
+        <v>15</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Goblin Diplomacy</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>100.3</t>
-        </is>
+      <c r="C165" t="n">
+        <v>103</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10642,20 +9620,16 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A166" t="n">
+        <v>101</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>100.3</t>
-        </is>
+      <c r="C166" t="n">
+        <v>103</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10667,20 +9641,16 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A167" t="n">
+        <v>26</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Fishing Contest</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>100.2</t>
-        </is>
+      <c r="C167" t="n">
+        <v>102</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10692,20 +9662,16 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A168" t="n">
+        <v>101</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>100.2</t>
-        </is>
+      <c r="C168" t="n">
+        <v>102</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10717,20 +9683,16 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A169" t="n">
+        <v>49</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Gertrude's Cat</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
+      <c r="C169" t="n">
+        <v>106</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10742,20 +9704,16 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A170" t="n">
+        <v>101</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
+      <c r="C170" t="n">
+        <v>106</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10767,20 +9725,16 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="A171" t="n">
+        <v>91</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Shadow of the Storm</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
+      <c r="C171" t="n">
+        <v>106</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10792,20 +9746,16 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A172" t="n">
+        <v>101</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>100.4</t>
-        </is>
+      <c r="C172" t="n">
+        <v>104</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10817,20 +9767,16 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A173" t="n">
+        <v>52</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Big Chompy Bird Hunting</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="C173" t="n">
+        <v>105</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10842,20 +9788,16 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A174" t="n">
+        <v>38</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Biohazard</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="C174" t="n">
+        <v>105</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10867,20 +9809,16 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A175" t="n">
+        <v>2</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="C175" t="n">
+        <v>105</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10892,20 +9830,16 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A176" t="n">
+        <v>47</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Murder Mystery</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="C176" t="n">
+        <v>105</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10917,20 +9851,16 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A177" t="n">
+        <v>55</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Nature Spirit</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="C177" t="n">
+        <v>105</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10942,20 +9872,16 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A178" t="n">
+        <v>101</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="C178" t="n">
+        <v>105</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -10967,20 +9893,16 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A179" t="n">
+        <v>20</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Witch's House</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="C179" t="n">
+        <v>105</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -10992,20 +9914,16 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A180" t="n">
+        <v>101</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>100.8</t>
-        </is>
+      <c r="C180" t="n">
+        <v>108</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11017,20 +9935,16 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A181" t="n">
+        <v>50</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Started:Legends' Quest</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>100.8</t>
-        </is>
+      <c r="C181" t="n">
+        <v>108</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11042,20 +9956,16 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="A182" t="n">
+        <v>65</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Monkey Madness I</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>100.7</t>
-        </is>
+      <c r="C182" t="n">
+        <v>107</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11067,20 +9977,16 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A183" t="n">
+        <v>101</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>100.7</t>
-        </is>
+      <c r="C183" t="n">
+        <v>107</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11092,20 +9998,16 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A184" t="n">
+        <v>52</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Big Chompy Bird Hunting</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="C184" t="n">
+        <v>109</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11117,20 +10019,16 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="A185" t="n">
+        <v>101</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Another Cook's Quest</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="C185" t="n">
+        <v>109</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11142,20 +10040,16 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="A186" t="n">
+        <v>120</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Darkness of Hallowvale</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="C186" t="n">
+        <v>148</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11167,20 +10061,16 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A187" t="n">
+        <v>18</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="C187" t="n">
+        <v>148</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11192,20 +10082,16 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A188" t="n">
+        <v>140</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Client of Kourend</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="C188" t="n">
+        <v>147</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11217,20 +10103,16 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="A189" t="n">
+        <v>128</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Cold War</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="C189" t="n">
+        <v>149</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11242,20 +10124,16 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="A190" t="n">
+        <v>123</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>My Arm's Big Adventure</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="C190" t="n">
+        <v>149</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11267,20 +10145,16 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A191" t="n">
+        <v>4</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Romeo &amp; Juliet</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="C191" t="n">
+        <v>149</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11292,20 +10166,16 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="A192" t="n">
+        <v>114</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Swan Song</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="C192" t="n">
+        <v>149</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11317,20 +10187,16 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A193" t="n">
+        <v>77</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Desert Treasure I</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C193" t="n">
+        <v>110</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11342,20 +10208,16 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A194" t="n">
+        <v>63</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Horror from the Deep</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C194" t="n">
+        <v>110</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11367,20 +10229,16 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>100.2</t>
-        </is>
+      <c r="A195" t="n">
+        <v>102</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing the Mountain Dwarf</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C195" t="n">
+        <v>110</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -11392,20 +10250,16 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>100.3</t>
-        </is>
+      <c r="A196" t="n">
+        <v>103</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing the Goblin generals</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C196" t="n">
+        <v>110</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -11417,20 +10271,16 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>100.4</t>
-        </is>
+      <c r="A197" t="n">
+        <v>104</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing Pirate Pete</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C197" t="n">
+        <v>110</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -11442,20 +10292,16 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
+      <c r="A198" t="n">
+        <v>105</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing the Lumbridge Guide</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C198" t="n">
+        <v>110</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -11467,20 +10313,16 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
+      <c r="A199" t="n">
+        <v>106</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing Evil Dave</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C199" t="n">
+        <v>110</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -11492,20 +10334,16 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="A200" t="n">
+        <v>109</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing Skrach Uglogwee</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C200" t="n">
+        <v>110</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -11517,20 +10355,16 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>100.8</t>
-        </is>
+      <c r="A201" t="n">
+        <v>108</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing Sir Amik Varze</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C201" t="n">
+        <v>110</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -11542,20 +10376,16 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>100.7</t>
-        </is>
+      <c r="A202" t="n">
+        <v>107</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Recipe for Disaster/Freeing King Awowogei</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
+      <c r="C202" t="n">
+        <v>110</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -11567,20 +10397,16 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A203" t="n">
+        <v>18</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="C203" t="n">
+        <v>153</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -11592,20 +10418,16 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="A204" t="n">
+        <v>92</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Making History</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="C204" t="n">
+        <v>153</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -11617,20 +10439,16 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="A205" t="n">
+        <v>89</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Mourning's End Part II</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="C205" t="n">
+        <v>153</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -11642,20 +10460,16 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A206" t="n">
+        <v>140</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Client of Kourend</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="C206" t="n">
+        <v>151</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -11667,20 +10481,16 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A207" t="n">
+        <v>140</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Client of Kourend</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+      <c r="C207" t="n">
+        <v>150</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -11692,20 +10502,16 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="A208" t="n">
+        <v>129</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>The Fremennik Isles</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="C208" t="n">
+        <v>154</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -11717,20 +10523,16 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="A209" t="n">
+        <v>118</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Lunar Diplomacy</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="C209" t="n">
+        <v>154</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -11742,20 +10544,16 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="A210" t="n">
+        <v>73</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Mountain Daughter</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="C210" t="n">
+        <v>154</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -11767,20 +10565,16 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A211" t="n">
+        <v>22</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Heroes' Quest</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="C211" t="n">
+        <v>154</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -11792,20 +10586,16 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A212" t="n">
+        <v>170</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Defender of Varrock</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="C212" t="n">
+        <v>180</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -11817,20 +10607,16 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="A213" t="n">
+        <v>67</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Troll Romance</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="C213" t="n">
+        <v>180</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -11842,20 +10628,16 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A214" t="n">
+        <v>6</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Shield of Arrav</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C214" t="n">
+        <v>170</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -11867,20 +10649,16 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A215" t="n">
+        <v>28</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Temple of Ikov</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C215" t="n">
+        <v>170</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -11892,20 +10670,16 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A216" t="n">
+        <v>158</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Below Ice Mountain</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C216" t="n">
+        <v>170</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -11917,20 +10691,16 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A217" t="n">
+        <v>24</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Family Crest</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C217" t="n">
+        <v>170</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -11942,20 +10712,16 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="A218" t="n">
+        <v>86</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Garden of Tranquillity</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C218" t="n">
+        <v>170</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -11967,20 +10733,16 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="A219" t="n">
+        <v>132</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>What Lies Below</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C219" t="n">
+        <v>170</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -11992,20 +10754,16 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A220" t="n">
+        <v>4</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Romeo &amp; Juliet</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C220" t="n">
+        <v>170</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -12017,20 +10775,16 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A221" t="n">
+        <v>2</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C221" t="n">
+        <v>170</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -12042,20 +10796,16 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="A222" t="n">
+        <v>148</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>A Taste of Hope</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="C222" t="n">
+        <v>155</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -12067,20 +10817,16 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A223" t="n">
+        <v>8</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Vampyre Slayer</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="C223" t="n">
+        <v>155</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -12098,10 +10844,8 @@
           <t>Architectural Alliance</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C224" t="n">
+        <v>160</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -12113,20 +10857,16 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="A225" t="n">
+        <v>151</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>The Ascent of Arceuus</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C225" t="n">
+        <v>160</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -12138,20 +10878,16 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="A226" t="n">
+        <v>144</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>The Depths of Despair</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C226" t="n">
+        <v>160</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -12163,20 +10899,16 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A227" t="n">
+        <v>18</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Druidic Ritual</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C227" t="n">
+        <v>160</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -12188,20 +10920,16 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+      <c r="A228" t="n">
+        <v>150</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>The Forsaken Tower</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C228" t="n">
+        <v>160</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -12213,20 +10941,16 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="A229" t="n">
+        <v>143</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>The Queen of Thieves</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C229" t="n">
+        <v>160</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -12238,20 +10962,16 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="A230" t="n">
+        <v>147</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Tale of the Righteous</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C230" t="n">
+        <v>160</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -12263,20 +10983,16 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="A231" t="n">
+        <v>148</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>A Taste of Hope</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="C231" t="n">
+        <v>159</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -12294,10 +11010,8 @@
           <t>Enter the Abyss</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="C232" t="n">
+        <v>162</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -12309,20 +11023,16 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A233" t="n">
+        <v>119</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>The Eyes of Glouphrie</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="C233" t="n">
+        <v>168</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -12334,20 +11044,16 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A234" t="n">
+        <v>37</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Waterfall Quest</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="C234" t="n">
+        <v>168</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -12359,20 +11065,16 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A235" t="n">
+        <v>31</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Tree Gnome Village</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="C235" t="n">
+        <v>168</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -12384,20 +11086,16 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A236" t="n">
+        <v>77</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Desert Treasure I</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="C236" t="n">
+        <v>167</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -12409,20 +11107,16 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="A237" t="n">
+        <v>166</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Secrets of the North</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="C237" t="n">
+        <v>167</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -12434,20 +11128,16 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="A238" t="n">
+        <v>97</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Enakhra's Lament</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="C238" t="n">
+        <v>167</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -12459,20 +11149,16 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="A239" t="n">
+        <v>162</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Temple of the Eye</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="C239" t="n">
+        <v>167</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -12484,20 +11170,16 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="A240" t="n">
+        <v>165</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>The Garden of Death</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="C240" t="n">
+        <v>167</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -12509,20 +11191,16 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A241" t="n">
+        <v>158</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Below Ice Mountain</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="C241" t="n">
+        <v>167</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -12540,10 +11218,8 @@
           <t>His Faithful Servants</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="C242" t="n">
+        <v>167</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -12555,20 +11231,16 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="A243" t="n">
+        <v>149</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Making Friends with My Arm</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="C243" t="n">
+        <v>166</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -12586,10 +11258,8 @@
           <t>The General's Shadow</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="C244" t="n">
+        <v>166</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -12601,20 +11271,16 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="A245" t="n">
+        <v>95</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Devious Minds</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="C245" t="n">
+        <v>166</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -12626,20 +11292,16 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A246" t="n">
+        <v>33</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Hazeel Cult</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="C246" t="n">
+        <v>166</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -12651,20 +11313,16 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A247" t="n">
+        <v>171</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Twilight's Promise</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="C247" t="n">
+        <v>173</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -12676,20 +11334,16 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A248" t="n">
+        <v>169</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Children of the Sun</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
+      <c r="C248" t="n">
+        <v>174</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -12701,20 +11355,16 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A249" t="n">
+        <v>169</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Children of the Sun</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="C249" t="n">
+        <v>171</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -12726,20 +11376,16 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A250" t="n">
+        <v>169</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Children of the Sun</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="C250" t="n">
+        <v>172</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -12751,20 +11397,16 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="A251" t="n">
+        <v>125</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Eagles' Peak</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="C251" t="n">
+        <v>172</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -12776,20 +11418,16 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A252" t="n">
+        <v>171</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Twilight's Promise</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
+      <c r="C252" t="n">
+        <v>176</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -12801,20 +11439,16 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A253" t="n">
+        <v>169</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Children of the Sun</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="C253" t="n">
+        <v>177</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -12826,20 +11460,16 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A254" t="n">
+        <v>169</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Children of the Sun</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="C254" t="n">
+        <v>178</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -12851,20 +11481,16 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A255" t="n">
+        <v>169</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Children of the Sun</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="C255" t="n">
+        <v>179</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -12876,20 +11502,16 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A256" t="n">
+        <v>6</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Shield of Arrav</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="C256" t="n">
+        <v>179</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
